--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BORRACHA PEDALEIRA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BORRACHA PEDALEIRA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BORRACHA PEDALEIRA TRASEIRA VHSV TITAN FAN160 181178</t>
+          <t>BORRACHA PEDALEIRA TRASEIRA PAR VHSV TITAN FAN160 181178</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BORRACHA PEDALEIRA ESTRIBO MOTOBOR+ BIZ100 44277</t>
+          <t>BORRACHA PEDALEIRA ESTRIBO PAR MOTOBOR+ BIZ100 44277</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +472,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BORRACHA PEDALEIRA ESTRIBO PEÇA+ BROS NXR150</t>
+          <t>BORRACHA PEDALEIRA ESTRIBO PAR PEÇA+ BROS NXR150</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +492,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BORRACHA PEDALEIRA ESTRIBO VEDOX BIZ</t>
+          <t>BORRACHA PEDALEIRA ESTRIBO PAR VEDOX BIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,17 +544,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BORRACHA ESTRIBO PEÇA+ YBR</t>
+          <t>BORRACHA ESTRIBO PAR PEÇA+ YBR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
     </row>
@@ -585,11 +570,6 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
     </row>
